--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -662,10 +662,8 @@
           <t>ITEM_ACQUIRE</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ITEM_TEMP_PASS</t>
-        </is>
+      <c r="D2" s="2" t="n">
+        <v>9001</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -705,10 +703,8 @@
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ITEM_JELLYPONG</t>
-        </is>
+      <c r="F3" s="3" t="n">
+        <v>1001</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -744,18 +740,14 @@
           <t>ITEM_COUNT</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ITEM_JELLYPONG</t>
-        </is>
+      <c r="D4" s="4" t="n">
+        <v>1001</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>ITEM_JELLYPONG</t>
-        </is>
+      <c r="F4" s="4" t="n">
+        <v>1001</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
@@ -787,10 +779,8 @@
       <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>ITEM_JELLYPONG</t>
-        </is>
+      <c r="F5" s="5" t="n">
+        <v>1001</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -830,10 +820,8 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ITEM_RABIJELLY</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>1002</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -869,18 +857,14 @@
           <t>ITEM_COUNT</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ITEM_RABIJELLY</t>
-        </is>
+      <c r="D7" s="4" t="n">
+        <v>1002</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>ITEM_RABIJELLY</t>
-        </is>
+      <c r="F7" s="4" t="n">
+        <v>1002</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -974,10 +958,8 @@
           <t>ITEM_ACQUIRE</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>ITEM_PASS_NORMAL</t>
-        </is>
+      <c r="D3" s="7" t="n">
+        <v>9002</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B215F7-703F-45C4-9B29-5BF9A8275E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76B9299-DEC1-4CDA-BED3-F5F74FE6B889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quest" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="79">
   <si>
     <t>QuestID</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>DialogueID</t>
-  </si>
-  <si>
-    <t>협회 방문</t>
   </si>
   <si>
     <t>ITEM_ACQUIRE</t>
@@ -259,6 +256,39 @@
   </si>
   <si>
     <t>VILLAGE1_GUILD_TALK_VFX</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모험가 협회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_REWARD</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -266,7 +296,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,6 +336,18 @@
       <sz val="10"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans KR"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="17">
@@ -418,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -469,6 +511,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -828,18 +885,14 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2">
-        <v>9001</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
+      <c r="B2" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2">
@@ -848,7 +901,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="20" customHeight="1">
@@ -856,13 +909,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -871,16 +924,16 @@
         <v>1001</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="3"/>
     </row>
@@ -889,10 +942,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="4">
         <v>1001</v>
@@ -904,7 +957,7 @@
         <v>1001</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
@@ -918,10 +971,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5">
@@ -931,7 +984,7 @@
         <v>1001</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="5">
         <v>2</v>
@@ -939,7 +992,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="20" customHeight="1">
@@ -947,13 +1000,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -962,16 +1015,16 @@
         <v>1002</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" s="3"/>
     </row>
@@ -980,10 +1033,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4">
         <v>1002</v>
@@ -995,7 +1048,7 @@
         <v>1002</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="4">
         <v>5</v>
@@ -1020,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -1033,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1044,29 +1097,57 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1">
       <c r="A3" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="7">
+        <v>28</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20" customHeight="1">
+      <c r="A4" s="6">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20" customHeight="1">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="7">
         <v>9002</v>
       </c>
     </row>
@@ -1095,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1">
@@ -1109,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20" customHeight="1">
@@ -1120,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
@@ -1131,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1">
@@ -1142,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20" customHeight="1">
@@ -1153,7 +1234,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20" customHeight="1">
@@ -1164,7 +1245,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20" customHeight="1">
@@ -1175,7 +1256,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20" customHeight="1">
@@ -1186,7 +1267,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20" customHeight="1">
@@ -1197,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20" customHeight="1">
@@ -1208,7 +1289,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20" customHeight="1">
@@ -1219,7 +1300,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20" customHeight="1">
@@ -1230,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20" customHeight="1">
@@ -1241,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20" customHeight="1">
@@ -1252,7 +1333,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20" customHeight="1">
@@ -1263,7 +1344,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20" customHeight="1">
@@ -1274,7 +1355,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20" customHeight="1">
@@ -1285,7 +1366,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1296,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1309,21 +1390,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1">
       <c r="A2" s="13">
-        <v>2</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="13">
+        <v>9001</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20" customHeight="1">
@@ -1331,38 +1412,49 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
       <c r="A4" s="13">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20" customHeight="1">
+      <c r="A5" s="13">
         <v>5</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20" customHeight="1">
+      <c r="A6" s="14">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="20" customHeight="1">
-      <c r="A5" s="14">
-        <v>5</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="C6" s="14" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B2:B500" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="B13:B500 B2:B8" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"UI_BUTTON,SUBQUEST_START"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1384,40 +1476,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.05" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="15"/>
     </row>
     <row r="2" spans="1:2" ht="16.05" customHeight="1">
       <c r="A2" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.05" customHeight="1">
       <c r="A3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1">
       <c r="A4" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.05" customHeight="1">
       <c r="A5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.05" customHeight="1">
@@ -1426,40 +1518,40 @@
     </row>
     <row r="7" spans="1:2" ht="16.05" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="15"/>
     </row>
     <row r="8" spans="1:2" ht="16.05" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16.05" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.05" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16.05" customHeight="1">
@@ -1468,32 +1560,32 @@
     </row>
     <row r="13" spans="1:2" ht="16.05" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="15"/>
     </row>
     <row r="14" spans="1:2" ht="16.05" customHeight="1">
       <c r="A14" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1">
       <c r="A15" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16.05" customHeight="1">
       <c r="A16" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.05" customHeight="1">
@@ -1502,24 +1594,24 @@
     </row>
     <row r="18" spans="1:2" ht="16.05" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="15"/>
     </row>
     <row r="19" spans="1:2" ht="16.05" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.05" customHeight="1">
@@ -1528,24 +1620,24 @@
     </row>
     <row r="22" spans="1:2" ht="16.05" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="15"/>
     </row>
     <row r="23" spans="1:2" ht="16.05" customHeight="1">
       <c r="A23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16.05" customHeight="1">
       <c r="A24" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16.05" customHeight="1">
@@ -1554,24 +1646,24 @@
     </row>
     <row r="26" spans="1:2" ht="16.05" customHeight="1">
       <c r="A26" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="15"/>
     </row>
     <row r="27" spans="1:2" ht="16.05" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16.05" customHeight="1">
       <c r="A28" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76B9299-DEC1-4CDA-BED3-F5F74FE6B889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD66A701-3B5F-4D88-BED1-54DC29DC44B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quest" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="82">
   <si>
     <t>QuestID</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>UI_BUTTON</t>
-  </si>
-  <si>
-    <t>BTN_BAG</t>
   </si>
   <si>
     <t>BTN_ALCHEMY</t>
@@ -289,6 +286,22 @@
   </si>
   <si>
     <t>ITEM_REWARD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GUILD_EXIT_QUEST_VFX</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BTN_CLICK</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNLOCK_INVENTORY_BUTTON</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNLOCK_TRAVEL_BUTTON</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -460,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -526,6 +539,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -886,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>21</v>
@@ -911,11 +930,11 @@
       <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
+      <c r="C3" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>78</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -1061,7 +1080,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2:C500" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"ITEM_ACQUIRE,ITEM_COUNT,ANIM_END,MULTI"</formula1>
+      <formula1>"ITEM_ACQUIRE,ITEM_COUNT,ANIM_END,MULTI,BTN_CLICK"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="J2:J500" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -1106,7 +1125,7 @@
         <v>28</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1">
@@ -1120,7 +1139,7 @@
         <v>28</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20" customHeight="1">
@@ -1190,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20" customHeight="1">
@@ -1201,7 +1220,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
@@ -1211,8 +1230,8 @@
       <c r="B4" s="9">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>32</v>
+      <c r="C4" s="23" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1">
@@ -1401,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" s="13">
         <v>9001</v>
@@ -1414,8 +1433,8 @@
       <c r="B3" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>41</v>
+      <c r="C3" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
@@ -1425,8 +1444,8 @@
       <c r="B4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>33</v>
+      <c r="C4" s="22" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1">
@@ -1437,7 +1456,7 @@
         <v>40</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20" customHeight="1">
@@ -1445,10 +1464,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1476,40 +1495,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.05" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="15"/>
     </row>
     <row r="2" spans="1:2" ht="16.05" customHeight="1">
       <c r="A2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>46</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.05" customHeight="1">
       <c r="A3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1">
       <c r="A4" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>50</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.05" customHeight="1">
       <c r="A5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>52</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.05" customHeight="1">
@@ -1518,7 +1537,7 @@
     </row>
     <row r="7" spans="1:2" ht="16.05" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="15"/>
     </row>
@@ -1527,7 +1546,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1">
@@ -1535,7 +1554,7 @@
         <v>19</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16.05" customHeight="1">
@@ -1543,7 +1562,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.05" customHeight="1">
@@ -1551,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16.05" customHeight="1">
@@ -1560,7 +1579,7 @@
     </row>
     <row r="13" spans="1:2" ht="16.05" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="15"/>
     </row>
@@ -1569,7 +1588,7 @@
         <v>28</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1">
@@ -1577,7 +1596,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16.05" customHeight="1">
@@ -1585,7 +1604,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.05" customHeight="1">
@@ -1594,7 +1613,7 @@
     </row>
     <row r="18" spans="1:2" ht="16.05" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="15"/>
     </row>
@@ -1603,15 +1622,15 @@
         <v>40</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.05" customHeight="1">
@@ -1620,24 +1639,24 @@
     </row>
     <row r="22" spans="1:2" ht="16.05" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="15"/>
     </row>
     <row r="23" spans="1:2" ht="16.05" customHeight="1">
       <c r="A23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16.05" customHeight="1">
       <c r="A24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>69</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16.05" customHeight="1">
@@ -1646,7 +1665,7 @@
     </row>
     <row r="26" spans="1:2" ht="16.05" customHeight="1">
       <c r="A26" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="15"/>
     </row>
@@ -1655,15 +1674,15 @@
         <v>37</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16.05" customHeight="1">
       <c r="A28" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>73</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD66A701-3B5F-4D88-BED1-54DC29DC44B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D409F946-98E2-4BBC-BC8A-7087B6508DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
   <si>
     <t>QuestID</t>
   </si>
@@ -936,18 +936,10 @@
       <c r="D3" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1001</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2</v>
-      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
         <v>15</v>
       </c>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D409F946-98E2-4BBC-BC8A-7087B6508DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5A7489-8A67-412D-9343-3453D0E4B46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5A7489-8A67-412D-9343-3453D0E4B46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F0085-E52B-4B2A-8843-6E8DAF16F8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quest" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="83">
   <si>
     <t>QuestID</t>
   </si>
@@ -304,6 +304,10 @@
     <t>UNLOCK_TRAVEL_BUTTON</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>VILLAGE1_TRAVEL_QUEST_VFX</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -322,6 +326,8 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -332,11 +338,15 @@
       <sz val="9"/>
       <color rgb="FF1A252F"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF444444"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
@@ -473,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -545,6 +555,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -850,7 +863,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -900,7 +913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1">
+    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -923,7 +936,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="20" customHeight="1">
+    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -948,7 +961,7 @@
       </c>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" ht="20" customHeight="1">
+    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -977,7 +990,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1">
+    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1006,7 +1019,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20" customHeight="1">
+    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1039,7 +1052,7 @@
       </c>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="20" customHeight="1">
+    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1085,7 +1098,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -1106,7 +1119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="20" customHeight="1">
+    <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1120,7 +1133,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="20" customHeight="1">
+    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -1134,7 +1147,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="20" customHeight="1">
+    <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -1148,7 +1161,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="20" customHeight="1">
+    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1176,7 +1189,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
@@ -1193,7 +1206,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20" customHeight="1">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -1204,7 +1217,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20" customHeight="1">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -1215,7 +1228,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20" customHeight="1">
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="9">
         <v>2</v>
       </c>
@@ -1226,18 +1239,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20" customHeight="1">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="10">
         <v>3</v>
       </c>
       <c r="B5" s="10">
         <v>1</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="20" customHeight="1">
+      <c r="C5" s="25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="10">
         <v>3</v>
       </c>
@@ -1248,7 +1261,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="20" customHeight="1">
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="10">
         <v>3</v>
       </c>
@@ -1259,7 +1272,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20" customHeight="1">
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -1270,7 +1283,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20" customHeight="1">
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="10">
         <v>3</v>
       </c>
@@ -1281,7 +1294,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="20" customHeight="1">
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="5">
         <v>4</v>
       </c>
@@ -1292,7 +1305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="20" customHeight="1">
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="5">
         <v>4</v>
       </c>
@@ -1303,7 +1316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="20" customHeight="1">
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="5">
         <v>4</v>
       </c>
@@ -1314,7 +1327,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1">
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="11">
         <v>5</v>
       </c>
@@ -1325,7 +1338,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="20" customHeight="1">
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="12">
         <v>6</v>
       </c>
@@ -1336,7 +1349,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="20" customHeight="1">
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="12">
         <v>6</v>
       </c>
@@ -1347,7 +1360,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="20" customHeight="1">
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="12">
         <v>6</v>
       </c>
@@ -1358,7 +1371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="20" customHeight="1">
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="12">
         <v>6</v>
       </c>
@@ -1369,7 +1382,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="20" customHeight="1">
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="12">
         <v>6</v>
       </c>
@@ -1389,7 +1402,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1407,7 +1420,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20" customHeight="1">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1418,7 +1431,7 @@
         <v>9001</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20" customHeight="1">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1429,7 +1442,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20" customHeight="1">
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="13">
         <v>2</v>
       </c>
@@ -1440,7 +1453,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20" customHeight="1">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -1451,7 +1464,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20" customHeight="1">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -1479,19 +1492,19 @@
     <tabColor rgb="FF888888"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.05" customHeight="1">
+    <row r="1" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="15"/>
     </row>
-    <row r="2" spans="1:2" ht="16.05" customHeight="1">
+    <row r="2" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>45</v>
       </c>
@@ -1499,7 +1512,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.05" customHeight="1">
+    <row r="3" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>47</v>
       </c>
@@ -1507,7 +1520,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.05" customHeight="1">
+    <row r="4" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="16" t="s">
         <v>49</v>
       </c>
@@ -1515,7 +1528,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.05" customHeight="1">
+    <row r="5" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>51</v>
       </c>
@@ -1523,17 +1536,17 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.05" customHeight="1">
+    <row r="6" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
     </row>
-    <row r="7" spans="1:2" ht="16.05" customHeight="1">
+    <row r="7" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B7" s="15"/>
     </row>
-    <row r="8" spans="1:2" ht="16.05" customHeight="1">
+    <row r="8" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A8" s="16" t="s">
         <v>11</v>
       </c>
@@ -1541,7 +1554,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16.05" customHeight="1">
+    <row r="9" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>19</v>
       </c>
@@ -1549,7 +1562,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.05" customHeight="1">
+    <row r="10" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A10" s="16" t="s">
         <v>14</v>
       </c>
@@ -1557,7 +1570,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16.05" customHeight="1">
+    <row r="11" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>21</v>
       </c>
@@ -1565,17 +1578,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.05" customHeight="1">
+    <row r="12" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
     </row>
-    <row r="13" spans="1:2" ht="16.05" customHeight="1">
+    <row r="13" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A13" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="15"/>
     </row>
-    <row r="14" spans="1:2" ht="16.05" customHeight="1">
+    <row r="14" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="16" t="s">
         <v>28</v>
       </c>
@@ -1583,7 +1596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16.05" customHeight="1">
+    <row r="15" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>11</v>
       </c>
@@ -1591,7 +1604,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16.05" customHeight="1">
+    <row r="16" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="16" t="s">
         <v>19</v>
       </c>
@@ -1599,17 +1612,17 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.05" customHeight="1">
+    <row r="17" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
     </row>
-    <row r="18" spans="1:2" ht="16.05" customHeight="1">
+    <row r="18" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>62</v>
       </c>
       <c r="B18" s="15"/>
     </row>
-    <row r="19" spans="1:2" ht="16.05" customHeight="1">
+    <row r="19" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A19" s="16" t="s">
         <v>40</v>
       </c>
@@ -1617,7 +1630,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.05" customHeight="1">
+    <row r="20" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A20" s="16" t="s">
         <v>42</v>
       </c>
@@ -1625,17 +1638,17 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16.05" customHeight="1">
+    <row r="21" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
     </row>
-    <row r="22" spans="1:2" ht="16.05" customHeight="1">
+    <row r="22" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A22" s="15" t="s">
         <v>65</v>
       </c>
       <c r="B22" s="15"/>
     </row>
-    <row r="23" spans="1:2" ht="16.05" customHeight="1">
+    <row r="23" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A23" s="16" t="s">
         <v>66</v>
       </c>
@@ -1643,7 +1656,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="16.05" customHeight="1">
+    <row r="24" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A24" s="16" t="s">
         <v>68</v>
       </c>
@@ -1651,17 +1664,17 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16.05" customHeight="1">
+    <row r="25" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
     </row>
-    <row r="26" spans="1:2" ht="16.05" customHeight="1">
+    <row r="26" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A26" s="15" t="s">
         <v>70</v>
       </c>
       <c r="B26" s="15"/>
     </row>
-    <row r="27" spans="1:2" ht="16.05" customHeight="1">
+    <row r="27" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A27" s="16" t="s">
         <v>37</v>
       </c>
@@ -1669,7 +1682,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16.05" customHeight="1">
+    <row r="28" spans="1:2" ht="16.149999999999999" customHeight="1">
       <c r="A28" s="16" t="s">
         <v>72</v>
       </c>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F0085-E52B-4B2A-8843-6E8DAF16F8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5A8B80-F080-42D2-8BB3-983B75579F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quest" sheetId="1" r:id="rId1"/>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="C2" s="13" t="n">
-        <v>9001</v>
+        <v>20001</v>
       </c>
     </row>
     <row r="3" ht="20.1" customHeight="1">

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest_Notify" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest_Unlock" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Ref" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubQuest_Main" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubQuest_Notify" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubQuest_Unlock_Table" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -632,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -879,7 +882,11 @@
         <v>5</v>
       </c>
       <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="n"/>
     </row>
     <row r="7" ht="20.1" customHeight="1">
@@ -916,6 +923,45 @@
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2급 모험가 완료 보고</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10002</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>폴짝 젤리</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GuildQuest3Text</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1020,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="2"/>
@@ -1262,6 +1308,45 @@
       <c r="C18" s="12" t="inlineStr">
         <is>
           <t>BTN_STAGE_BREEZING_WIND_FOREST_ENTRANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1372,6 +1457,58 @@
         <is>
           <t>SUBQUEST_1</t>
         </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20002</v>
       </c>
     </row>
   </sheetData>
@@ -1673,4 +1810,239 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SubQuestID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SubQuestName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CompleteType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CompleteParam</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DialogueID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>연금공방 첫 방문</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BTN_ALCHEMY_TALK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AlchemyQuest1Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>서브퀘스트 완료</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SubQuestID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TargetID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ShowTiming</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BTN_ALCHEMY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ON_START</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BTN_ALCHEMY_TALK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ON_START</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SubQuestID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>QuestType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>UnlockType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TargetID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>UnlockValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SUB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>UI_BUTTON</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BTN_COMMISION</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SUB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UI_BUTTON</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UNLOCK_POTION_BUTTON</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,1590 @@
         <is>
           <t>GuildQuest3Text</t>
         </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>속삭이는 동굴 조사</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11001</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>슬라임 젤리</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>속삭이는 동굴 완료 보고</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11001</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>슬라임 젤리</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>폐허가 된 성소 조사</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11004</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11004</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>독버섯 갓</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>폐허가 된 성소 완료 보고</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11004</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>독버섯 갓</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>가라앉은 숲 조사</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11007</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11007</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>까마귀 깃털</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>가라앉은 숲 완료 보고</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11007</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>까마귀 깃털</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>텅 빈 굴 조사</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11001</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>슬라임 젤리</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>텅 빈 굴 완료 보고</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11001</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>슬라임 젤리</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>소금 늪지 조사</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11003</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11003</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>늑대 송곳니</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>소금 늪지 완료 보고</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11003</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>늑대 송곳니</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>밀물 동굴 조사</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11006</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11006</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>멧돼지 가죽</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>밀물 동굴 완료 보고</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11006</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>멧돼지 가죽</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>부서진 잔교 조사</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11002</v>
+      </c>
+      <c r="E21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11002</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>거미 실크</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>부서진 잔교 완료 보고</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11002</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>거미 실크</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>폭풍 절벽 조사</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11005</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11005</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>바람 정수</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>폭풍 절벽 완료 보고</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11005</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>바람 정수</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>표류목 숲 조사</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11018</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11018</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>그림자 응결물</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>표류목 숲 완료 보고</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11018</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>그림자 응결물</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>잿불 구덩이 조사</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11011</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" t="n">
+        <v>11011</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>박쥐 날개막</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>잿불 구덩이 완료 보고</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11011</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>박쥐 날개막</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>깊은 수직굴 조사</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11014</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" t="n">
+        <v>11014</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>수정 파편</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>깊은 수직굴 완료 보고</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11014</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>수정 파편</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>녹슨 회랑 조사</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11017</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11017</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>석상 조각</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>녹슨 회랑 완료 보고</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>11017</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>석상 조각</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>불씨 광맥 조사</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11013</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11013</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>광부의 유품</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>불씨 광맥 완료 보고</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11013</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>광부의 유품</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>무너진 갱도 조사</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11016</v>
+      </c>
+      <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11016</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>젖은 이끼</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>무너진 갱도 완료 보고</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11016</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>젖은 이끼</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>서리 수림 조사</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11011</v>
+      </c>
+      <c r="E37" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11011</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>박쥐 날개막</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>서리 수림 완료 보고</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11011</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>박쥐 날개막</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>빙하 동굴 조사</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11012</v>
+      </c>
+      <c r="E39" t="n">
+        <v>21</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11012</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>두더지 발톱</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>빙하 동굴 완료 보고</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11012</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>두더지 발톱</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>고요한 예배당 조사</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11021</v>
+      </c>
+      <c r="E41" t="n">
+        <v>23</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11021</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>망령의 재</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>고요한 예배당 완료 보고</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11021</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>망령의 재</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>새하얀 황야 조사</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11022</v>
+      </c>
+      <c r="E43" t="n">
+        <v>23</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11022</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>기사의 문장</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>새하얀 황야 완료 보고</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>11022</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>기사의 문장</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고 조사</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11026</v>
+      </c>
+      <c r="E45" t="n">
+        <v>25</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11026</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>수호자의 핵</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고 완료 보고</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>11026</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>수호자의 핵</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>여명의 정원 조사</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11021</v>
+      </c>
+      <c r="E47" t="n">
+        <v>27</v>
+      </c>
+      <c r="F47" t="n">
+        <v>11021</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>망령의 재</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>여명의 정원 완료 보고</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11021</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>망령의 재</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>공허의 계단 조사</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11024</v>
+      </c>
+      <c r="E49" t="n">
+        <v>27</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11024</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>키메라 갈기</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>공허의 계단 완료 보고</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>11024</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>키메라 갈기</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>별의 성소 조사</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11022</v>
+      </c>
+      <c r="E51" t="n">
+        <v>29</v>
+      </c>
+      <c r="F51" t="n">
+        <v>11022</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>기사의 문장</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>별의 성소 완료 보고</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>11022</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>기사의 문장</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>마지막 성벽 조사</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11026</v>
+      </c>
+      <c r="E53" t="n">
+        <v>29</v>
+      </c>
+      <c r="F53" t="n">
+        <v>11026</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>수호자의 핵</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>마지막 성벽 완료 보고</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11026</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>수호자의 핵</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>여명의 왕좌 조사</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ITEM_COUNT</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11021</v>
+      </c>
+      <c r="E55" t="n">
+        <v>31</v>
+      </c>
+      <c r="F55" t="n">
+        <v>11021</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>망령의 재</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>여명의 왕좌 완료 보고</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTN_CLICK</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>11021</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>망령의 재</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="2"/>
@@ -1345,6 +2929,2190 @@
         <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUMD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SUNKENGROVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SUNKENGROVED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>13</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>14</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BTN_MAP_HOLLOWBURROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>14</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_HOLLOWBURROWD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>15</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>15</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>16</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>16</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>16</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SALTMARSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SALTMARSHD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>17</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>17</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>18</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>18</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>18</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BTN_MAP_TIDALCAVERN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>18</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_TIDALCAVERND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>19</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>19</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>19</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>20</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>20</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BROKENPIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>20</v>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BROKENPIERD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>21</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>21</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>21</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>22</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>22</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>22</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STORMCLIFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>22</v>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STORMCLIFFD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>23</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>23</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>23</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>24</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>24</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>24</v>
+      </c>
+      <c r="B80" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DRIFTWOODWOOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>24</v>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DRIFTWOODWOODD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>25</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>25</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>25</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>26</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>26</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>26</v>
+      </c>
+      <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTN_MAP_CINDERPIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>26</v>
+      </c>
+      <c r="B88" t="n">
+        <v>4</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_CINDERPITD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>27</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>27</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>27</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>28</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>28</v>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>28</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DEEPSHAFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>28</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DEEPSHAFTD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>29</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>29</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>29</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>30</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>30</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>30</v>
+      </c>
+      <c r="B101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUSTHALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>30</v>
+      </c>
+      <c r="B102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUSTHALLD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>31</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>31</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>31</v>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>32</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>32</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>32</v>
+      </c>
+      <c r="B108" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BTN_MAP_EMBERVEIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>32</v>
+      </c>
+      <c r="B109" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_EMBERVEIND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>33</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>33</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>33</v>
+      </c>
+      <c r="B112" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>34</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>34</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>34</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BTN_MAP_COLLAPSEDTUNNEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>34</v>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_COLLAPSEDTUNNELD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>35</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>35</v>
+      </c>
+      <c r="B118" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>35</v>
+      </c>
+      <c r="B119" t="n">
+        <v>3</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>36</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>36</v>
+      </c>
+      <c r="B121" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>36</v>
+      </c>
+      <c r="B122" t="n">
+        <v>3</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROSTWOOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>36</v>
+      </c>
+      <c r="B123" t="n">
+        <v>4</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROSTWOODD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>37</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>37</v>
+      </c>
+      <c r="B125" t="n">
+        <v>2</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>37</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>38</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>38</v>
+      </c>
+      <c r="B128" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>38</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BTN_MAP_GLACIERCAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>38</v>
+      </c>
+      <c r="B130" t="n">
+        <v>4</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_GLACIERCAVED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>39</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>39</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>39</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>40</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>40</v>
+      </c>
+      <c r="B135" t="n">
+        <v>2</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>40</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SILENTCHAPEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>40</v>
+      </c>
+      <c r="B137" t="n">
+        <v>4</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SILENTCHAPELD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>41</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>41</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>41</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>42</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>42</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>42</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHITEWASTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>42</v>
+      </c>
+      <c r="B144" t="n">
+        <v>4</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHITEWASTED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>43</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>43</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>43</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>44</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>44</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>44</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROZENVAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>44</v>
+      </c>
+      <c r="B151" t="n">
+        <v>4</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROZENVAULTD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>45</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>45</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>45</v>
+      </c>
+      <c r="B154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>46</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>46</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>46</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DAWNGARDEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>46</v>
+      </c>
+      <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DAWNGARDEND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>47</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>47</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>47</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>48</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>48</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>48</v>
+      </c>
+      <c r="B164" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BTN_MAP_VOIDSTAIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>48</v>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_VOIDSTAIRD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>49</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>49</v>
+      </c>
+      <c r="B167" t="n">
+        <v>2</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>49</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>50</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>50</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>50</v>
+      </c>
+      <c r="B171" t="n">
+        <v>3</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STARSANCTUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>50</v>
+      </c>
+      <c r="B172" t="n">
+        <v>4</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STARSANCTUMD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>51</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>51</v>
+      </c>
+      <c r="B174" t="n">
+        <v>2</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>51</v>
+      </c>
+      <c r="B175" t="n">
+        <v>3</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>52</v>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>52</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>52</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BTN_MAP_LASTRAMPART</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>52</v>
+      </c>
+      <c r="B179" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_LASTRAMPARTD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>53</v>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>53</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>53</v>
+      </c>
+      <c r="B182" t="n">
+        <v>3</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BTN_GUILD_QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>54</v>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BTN_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>54</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BTN_EXPLORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>54</v>
+      </c>
+      <c r="B185" t="n">
+        <v>3</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BTN_MAP_THRONEOFDAWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>54</v>
+      </c>
+      <c r="B186" t="n">
+        <v>4</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_THRONEOFDAWND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>55</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BTN_BATTLE_SCENE_JOURNEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>55</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BTN_GUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>55</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3</v>
+      </c>
+      <c r="C189" t="inlineStr">
         <is>
           <t>BTN_GUILD_QUEST</t>
         </is>
@@ -1361,7 +5129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1509,6 +5277,630 @@
       </c>
       <c r="C10" t="n">
         <v>20002</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>11004</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>11007</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>11003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>11006</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>11005</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>11018</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>11011</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>11017</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>11013</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>11016</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11011</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>11012</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>11021</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>11022</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>11026</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>11021</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>11024</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>11022</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>11026</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ITEM_REMOVE</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>11021</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ITEM_REWARD</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10013</v>
       </c>
     </row>
   </sheetData>
@@ -1887,8 +6279,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -1028,6 +1028,11 @@
       <c r="H10" t="n">
         <v>3</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>GuildQuest4Text</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1094,6 +1099,11 @@
       <c r="H12" t="n">
         <v>5</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>GuildQuest5Text</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1160,6 +1170,11 @@
       <c r="H14" t="n">
         <v>5</v>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>GuildQuest6Text</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1226,6 +1241,11 @@
       <c r="H16" t="n">
         <v>7</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>GuildQuest7Text</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1292,6 +1312,11 @@
       <c r="H18" t="n">
         <v>9</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>GuildQuest8Text</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1358,6 +1383,11 @@
       <c r="H20" t="n">
         <v>9</v>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>GuildQuest9Text</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1424,6 +1454,11 @@
       <c r="H22" t="n">
         <v>11</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>GuildQuest10Text</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1490,6 +1525,11 @@
       <c r="H24" t="n">
         <v>11</v>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>GuildQuest11Text</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1556,6 +1596,11 @@
       <c r="H26" t="n">
         <v>13</v>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>GuildQuest12Text</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1622,6 +1667,11 @@
       <c r="H28" t="n">
         <v>15</v>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>GuildQuest13Text</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1688,6 +1738,11 @@
       <c r="H30" t="n">
         <v>15</v>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>GuildQuest14Text</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1754,6 +1809,11 @@
       <c r="H32" t="n">
         <v>17</v>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>GuildQuest15Text</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1820,6 +1880,11 @@
       <c r="H34" t="n">
         <v>17</v>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>GuildQuest16Text</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1886,6 +1951,11 @@
       <c r="H36" t="n">
         <v>19</v>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>GuildQuest17Text</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1952,6 +2022,11 @@
       <c r="H38" t="n">
         <v>21</v>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>GuildQuest18Text</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2018,6 +2093,11 @@
       <c r="H40" t="n">
         <v>21</v>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>GuildQuest19Text</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2084,6 +2164,11 @@
       <c r="H42" t="n">
         <v>23</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>GuildQuest20Text</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2150,6 +2235,11 @@
       <c r="H44" t="n">
         <v>23</v>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>GuildQuest21Text</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2216,6 +2306,11 @@
       <c r="H46" t="n">
         <v>25</v>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>GuildQuest22Text</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2282,6 +2377,11 @@
       <c r="H48" t="n">
         <v>27</v>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>GuildQuest23Text</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2348,6 +2448,11 @@
       <c r="H50" t="n">
         <v>27</v>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>GuildQuest24Text</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2414,6 +2519,11 @@
       <c r="H52" t="n">
         <v>29</v>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>GuildQuest25Text</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2480,6 +2590,11 @@
       <c r="H54" t="n">
         <v>29</v>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>GuildQuest26Text</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2545,6 +2660,11 @@
       </c>
       <c r="H56" t="n">
         <v>31</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>GuildQuest27Text</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/QuestData.xlsx
+++ b/Assets/@Resources/Data/Excel/QuestData.xlsx
@@ -5249,7 +5249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6021,6 +6021,51 @@
       </c>
       <c r="C58" t="n">
         <v>10013</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UI_BUTTON</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>UNLOCK_FORGE_BUTTON</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UI_BUTTON</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>UNLOCK_SHOP_BUTTON</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>11</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UI_BUTTON</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UNLOCK_MONASTERY_BUTTON</t>
+        </is>
       </c>
     </row>
   </sheetData>
